--- a/DATRAS/MasterTable.xlsx
+++ b/DATRAS/MasterTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wageningenur4-my.sharepoint.com/personal/lennert_vandepol_wur_nl/Documents/Git/Lab/wg_WGCEPH/DATRAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{AFC1A10A-2DE6-4D70-BB57-E8EF3423DAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEC244C4-EAE0-4C8F-B076-9A63BDEEBE70}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{AFC1A10A-2DE6-4D70-BB57-E8EF3423DAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38352814-A6F7-4C80-9092-B6BCC75A4347}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D4280C1B-7790-4CE2-8B71-8148A0476AE1}"/>
   </bookViews>
@@ -696,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CD9828C-51DD-45A3-B37A-6F9A2A634A96}">
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
@@ -2165,7 +2165,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>57</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>57</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>57</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>57</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>57</v>
       </c>
@@ -2280,7 +2280,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>57</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>57</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>57</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>57</v>
       </c>
@@ -2372,693 +2372,693 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C74" t="s">
+        <v>76</v>
+      </c>
+      <c r="D74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" t="s">
+        <v>37</v>
+      </c>
+      <c r="F74" t="s">
+        <v>77</v>
+      </c>
+      <c r="G74" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
         <v>75</v>
       </c>
-      <c r="D74" t="s">
+      <c r="C75" t="s">
         <v>76</v>
       </c>
-      <c r="E74" t="s">
-        <v>20</v>
-      </c>
-      <c r="F74" t="s">
-        <v>37</v>
-      </c>
-      <c r="G74" t="s">
-        <v>77</v>
-      </c>
-      <c r="H74" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B75" t="s">
-        <v>74</v>
-      </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
+        <v>25</v>
+      </c>
+      <c r="E75" t="s">
+        <v>26</v>
+      </c>
+      <c r="F75" t="s">
+        <v>79</v>
+      </c>
+      <c r="G75" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>74</v>
+      </c>
+      <c r="B76" t="s">
         <v>75</v>
       </c>
-      <c r="D75" t="s">
+      <c r="C76" t="s">
         <v>76</v>
       </c>
-      <c r="E75" t="s">
-        <v>25</v>
-      </c>
-      <c r="F75" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" t="s">
-        <v>79</v>
-      </c>
-      <c r="H75" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B76" t="s">
-        <v>74</v>
-      </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
+        <v>21</v>
+      </c>
+      <c r="E76" t="s">
+        <v>30</v>
+      </c>
+      <c r="F76" t="s">
+        <v>43</v>
+      </c>
+      <c r="G76" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>74</v>
+      </c>
+      <c r="B77" t="s">
         <v>75</v>
       </c>
-      <c r="D76" t="s">
+      <c r="C77" t="s">
         <v>76</v>
       </c>
-      <c r="E76" t="s">
-        <v>21</v>
-      </c>
-      <c r="F76" t="s">
-        <v>30</v>
-      </c>
-      <c r="G76" t="s">
-        <v>43</v>
-      </c>
-      <c r="H76" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B77" t="s">
-        <v>74</v>
-      </c>
-      <c r="C77" t="s">
-        <v>75</v>
-      </c>
       <c r="D77" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="E77" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F77" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G77" t="s">
         <v>44</v>
       </c>
-      <c r="H77" t="s">
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>74</v>
+      </c>
+      <c r="B78" t="s">
+        <v>75</v>
+      </c>
+      <c r="C78" t="s">
+        <v>76</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E78" t="s">
+        <v>34</v>
+      </c>
+      <c r="F78" t="s">
+        <v>35</v>
+      </c>
+      <c r="G78" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>74</v>
+      </c>
+      <c r="B79" t="s">
+        <v>81</v>
+      </c>
+      <c r="C79" t="s">
+        <v>82</v>
+      </c>
+      <c r="D79" t="s">
+        <v>20</v>
+      </c>
+      <c r="E79" t="s">
+        <v>37</v>
+      </c>
+      <c r="F79" t="s">
+        <v>77</v>
+      </c>
+      <c r="G79" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>74</v>
+      </c>
+      <c r="B80" t="s">
+        <v>81</v>
+      </c>
+      <c r="C80" t="s">
+        <v>82</v>
+      </c>
+      <c r="D80" t="s">
+        <v>25</v>
+      </c>
+      <c r="E80" t="s">
+        <v>26</v>
+      </c>
+      <c r="F80" t="s">
+        <v>79</v>
+      </c>
+      <c r="G80" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>74</v>
+      </c>
+      <c r="B81" t="s">
+        <v>81</v>
+      </c>
+      <c r="C81" t="s">
+        <v>82</v>
+      </c>
+      <c r="D81" t="s">
+        <v>21</v>
+      </c>
+      <c r="E81" t="s">
+        <v>30</v>
+      </c>
+      <c r="F81" t="s">
+        <v>43</v>
+      </c>
+      <c r="G81" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>74</v>
+      </c>
+      <c r="B82" t="s">
+        <v>81</v>
+      </c>
+      <c r="C82" t="s">
+        <v>82</v>
+      </c>
+      <c r="D82" t="s">
+        <v>22</v>
+      </c>
+      <c r="E82" t="s">
+        <v>32</v>
+      </c>
+      <c r="F82" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B78" t="s">
-        <v>74</v>
-      </c>
-      <c r="C78" t="s">
-        <v>75</v>
-      </c>
-      <c r="D78" t="s">
-        <v>76</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F78" t="s">
-        <v>34</v>
-      </c>
-      <c r="G78" t="s">
-        <v>35</v>
-      </c>
-      <c r="H78" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B79" t="s">
-        <v>74</v>
-      </c>
-      <c r="C79" t="s">
-        <v>81</v>
-      </c>
-      <c r="D79" t="s">
-        <v>82</v>
-      </c>
-      <c r="E79" t="s">
-        <v>20</v>
-      </c>
-      <c r="F79" t="s">
-        <v>37</v>
-      </c>
-      <c r="G79" t="s">
-        <v>77</v>
-      </c>
-      <c r="H79" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B80" t="s">
-        <v>74</v>
-      </c>
-      <c r="C80" t="s">
-        <v>81</v>
-      </c>
-      <c r="D80" t="s">
-        <v>82</v>
-      </c>
-      <c r="E80" t="s">
-        <v>25</v>
-      </c>
-      <c r="F80" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" t="s">
-        <v>79</v>
-      </c>
-      <c r="H80" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B81" t="s">
-        <v>74</v>
-      </c>
-      <c r="C81" t="s">
-        <v>81</v>
-      </c>
-      <c r="D81" t="s">
-        <v>82</v>
-      </c>
-      <c r="E81" t="s">
-        <v>21</v>
-      </c>
-      <c r="F81" t="s">
-        <v>30</v>
-      </c>
-      <c r="G81" t="s">
-        <v>43</v>
-      </c>
-      <c r="H81" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B82" t="s">
-        <v>74</v>
-      </c>
-      <c r="C82" t="s">
-        <v>81</v>
-      </c>
-      <c r="D82" t="s">
-        <v>82</v>
-      </c>
-      <c r="E82" t="s">
-        <v>22</v>
-      </c>
-      <c r="F82" t="s">
-        <v>32</v>
       </c>
       <c r="G82" t="s">
         <v>44</v>
       </c>
-      <c r="H82" t="s">
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>74</v>
+      </c>
+      <c r="B83" t="s">
+        <v>81</v>
+      </c>
+      <c r="C83" t="s">
+        <v>82</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E83" t="s">
+        <v>34</v>
+      </c>
+      <c r="F83" t="s">
+        <v>35</v>
+      </c>
+      <c r="G83" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>74</v>
+      </c>
+      <c r="B84" t="s">
+        <v>83</v>
+      </c>
+      <c r="C84" t="s">
+        <v>84</v>
+      </c>
+      <c r="D84" t="s">
+        <v>20</v>
+      </c>
+      <c r="E84" t="s">
+        <v>37</v>
+      </c>
+      <c r="F84" t="s">
+        <v>77</v>
+      </c>
+      <c r="G84" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>74</v>
+      </c>
+      <c r="B85" t="s">
+        <v>83</v>
+      </c>
+      <c r="C85" t="s">
+        <v>84</v>
+      </c>
+      <c r="D85" t="s">
+        <v>25</v>
+      </c>
+      <c r="E85" t="s">
+        <v>26</v>
+      </c>
+      <c r="F85" t="s">
+        <v>79</v>
+      </c>
+      <c r="G85" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>74</v>
+      </c>
+      <c r="B86" t="s">
+        <v>83</v>
+      </c>
+      <c r="C86" t="s">
+        <v>84</v>
+      </c>
+      <c r="D86" t="s">
+        <v>21</v>
+      </c>
+      <c r="E86" t="s">
+        <v>30</v>
+      </c>
+      <c r="F86" t="s">
+        <v>43</v>
+      </c>
+      <c r="G86" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>74</v>
+      </c>
+      <c r="B87" t="s">
+        <v>83</v>
+      </c>
+      <c r="C87" t="s">
+        <v>84</v>
+      </c>
+      <c r="D87" t="s">
+        <v>22</v>
+      </c>
+      <c r="E87" t="s">
+        <v>32</v>
+      </c>
+      <c r="F87" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B83" t="s">
-        <v>74</v>
-      </c>
-      <c r="C83" t="s">
-        <v>81</v>
-      </c>
-      <c r="D83" t="s">
-        <v>82</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F83" t="s">
-        <v>34</v>
-      </c>
-      <c r="G83" t="s">
-        <v>35</v>
-      </c>
-      <c r="H83" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B84" t="s">
-        <v>74</v>
-      </c>
-      <c r="C84" t="s">
-        <v>83</v>
-      </c>
-      <c r="D84" t="s">
-        <v>84</v>
-      </c>
-      <c r="E84" t="s">
-        <v>20</v>
-      </c>
-      <c r="F84" t="s">
-        <v>37</v>
-      </c>
-      <c r="G84" t="s">
-        <v>77</v>
-      </c>
-      <c r="H84" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B85" t="s">
-        <v>74</v>
-      </c>
-      <c r="C85" t="s">
-        <v>83</v>
-      </c>
-      <c r="D85" t="s">
-        <v>84</v>
-      </c>
-      <c r="E85" t="s">
-        <v>25</v>
-      </c>
-      <c r="F85" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" t="s">
-        <v>79</v>
-      </c>
-      <c r="H85" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B86" t="s">
-        <v>74</v>
-      </c>
-      <c r="C86" t="s">
-        <v>83</v>
-      </c>
-      <c r="D86" t="s">
-        <v>84</v>
-      </c>
-      <c r="E86" t="s">
-        <v>21</v>
-      </c>
-      <c r="F86" t="s">
-        <v>30</v>
-      </c>
-      <c r="G86" t="s">
-        <v>43</v>
-      </c>
-      <c r="H86" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B87" t="s">
-        <v>74</v>
-      </c>
-      <c r="C87" t="s">
-        <v>83</v>
-      </c>
-      <c r="D87" t="s">
-        <v>84</v>
-      </c>
-      <c r="E87" t="s">
-        <v>22</v>
-      </c>
-      <c r="F87" t="s">
-        <v>32</v>
       </c>
       <c r="G87" t="s">
         <v>44</v>
       </c>
-      <c r="H87" t="s">
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>74</v>
+      </c>
+      <c r="B88" t="s">
+        <v>83</v>
+      </c>
+      <c r="C88" t="s">
+        <v>84</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E88" t="s">
+        <v>34</v>
+      </c>
+      <c r="F88" t="s">
+        <v>35</v>
+      </c>
+      <c r="G88" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>74</v>
+      </c>
+      <c r="B89" t="s">
+        <v>74</v>
+      </c>
+      <c r="C89" t="s">
+        <v>85</v>
+      </c>
+      <c r="D89" t="s">
+        <v>20</v>
+      </c>
+      <c r="E89" t="s">
+        <v>37</v>
+      </c>
+      <c r="F89" t="s">
+        <v>77</v>
+      </c>
+      <c r="G89" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>74</v>
+      </c>
+      <c r="B90" t="s">
+        <v>74</v>
+      </c>
+      <c r="C90" t="s">
+        <v>85</v>
+      </c>
+      <c r="D90" t="s">
+        <v>25</v>
+      </c>
+      <c r="E90" t="s">
+        <v>26</v>
+      </c>
+      <c r="F90" t="s">
+        <v>79</v>
+      </c>
+      <c r="G90" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>74</v>
+      </c>
+      <c r="B91" t="s">
+        <v>74</v>
+      </c>
+      <c r="C91" t="s">
+        <v>85</v>
+      </c>
+      <c r="D91" t="s">
+        <v>21</v>
+      </c>
+      <c r="E91" t="s">
+        <v>30</v>
+      </c>
+      <c r="F91" t="s">
+        <v>43</v>
+      </c>
+      <c r="G91" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>74</v>
+      </c>
+      <c r="B92" t="s">
+        <v>74</v>
+      </c>
+      <c r="C92" t="s">
+        <v>85</v>
+      </c>
+      <c r="D92" t="s">
+        <v>22</v>
+      </c>
+      <c r="E92" t="s">
+        <v>32</v>
+      </c>
+      <c r="F92" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B88" t="s">
-        <v>74</v>
-      </c>
-      <c r="C88" t="s">
-        <v>83</v>
-      </c>
-      <c r="D88" t="s">
-        <v>84</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F88" t="s">
-        <v>34</v>
-      </c>
-      <c r="G88" t="s">
-        <v>35</v>
-      </c>
-      <c r="H88" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B89" t="s">
-        <v>74</v>
-      </c>
-      <c r="C89" t="s">
-        <v>74</v>
-      </c>
-      <c r="D89" t="s">
-        <v>85</v>
-      </c>
-      <c r="E89" t="s">
-        <v>20</v>
-      </c>
-      <c r="F89" t="s">
-        <v>37</v>
-      </c>
-      <c r="G89" t="s">
-        <v>77</v>
-      </c>
-      <c r="H89" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B90" t="s">
-        <v>74</v>
-      </c>
-      <c r="C90" t="s">
-        <v>74</v>
-      </c>
-      <c r="D90" t="s">
-        <v>85</v>
-      </c>
-      <c r="E90" t="s">
-        <v>25</v>
-      </c>
-      <c r="F90" t="s">
-        <v>26</v>
-      </c>
-      <c r="G90" t="s">
-        <v>79</v>
-      </c>
-      <c r="H90" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B91" t="s">
-        <v>74</v>
-      </c>
-      <c r="C91" t="s">
-        <v>74</v>
-      </c>
-      <c r="D91" t="s">
-        <v>85</v>
-      </c>
-      <c r="E91" t="s">
-        <v>21</v>
-      </c>
-      <c r="F91" t="s">
-        <v>30</v>
-      </c>
-      <c r="G91" t="s">
-        <v>43</v>
-      </c>
-      <c r="H91" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B92" t="s">
-        <v>74</v>
-      </c>
-      <c r="C92" t="s">
-        <v>74</v>
-      </c>
-      <c r="D92" t="s">
-        <v>85</v>
-      </c>
-      <c r="E92" t="s">
-        <v>22</v>
-      </c>
-      <c r="F92" t="s">
-        <v>32</v>
       </c>
       <c r="G92" t="s">
         <v>44</v>
       </c>
-      <c r="H92" t="s">
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>74</v>
+      </c>
+      <c r="B93" t="s">
+        <v>74</v>
+      </c>
+      <c r="C93" t="s">
+        <v>85</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E93" t="s">
+        <v>34</v>
+      </c>
+      <c r="F93" t="s">
+        <v>35</v>
+      </c>
+      <c r="G93" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>74</v>
+      </c>
+      <c r="B94" t="s">
+        <v>86</v>
+      </c>
+      <c r="C94" t="s">
+        <v>87</v>
+      </c>
+      <c r="D94" t="s">
+        <v>20</v>
+      </c>
+      <c r="E94" t="s">
+        <v>37</v>
+      </c>
+      <c r="F94" t="s">
+        <v>77</v>
+      </c>
+      <c r="G94" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>74</v>
+      </c>
+      <c r="B95" t="s">
+        <v>86</v>
+      </c>
+      <c r="C95" t="s">
+        <v>87</v>
+      </c>
+      <c r="D95" t="s">
+        <v>25</v>
+      </c>
+      <c r="E95" t="s">
+        <v>26</v>
+      </c>
+      <c r="F95" t="s">
+        <v>79</v>
+      </c>
+      <c r="G95" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>74</v>
+      </c>
+      <c r="B96" t="s">
+        <v>86</v>
+      </c>
+      <c r="C96" t="s">
+        <v>87</v>
+      </c>
+      <c r="D96" t="s">
+        <v>21</v>
+      </c>
+      <c r="E96" t="s">
+        <v>30</v>
+      </c>
+      <c r="F96" t="s">
+        <v>43</v>
+      </c>
+      <c r="G96" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>74</v>
+      </c>
+      <c r="B97" t="s">
+        <v>86</v>
+      </c>
+      <c r="C97" t="s">
+        <v>87</v>
+      </c>
+      <c r="D97" t="s">
+        <v>22</v>
+      </c>
+      <c r="E97" t="s">
+        <v>32</v>
+      </c>
+      <c r="F97" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B93" t="s">
-        <v>74</v>
-      </c>
-      <c r="C93" t="s">
-        <v>74</v>
-      </c>
-      <c r="D93" t="s">
-        <v>85</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F93" t="s">
-        <v>34</v>
-      </c>
-      <c r="G93" t="s">
-        <v>35</v>
-      </c>
-      <c r="H93" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B94" t="s">
-        <v>74</v>
-      </c>
-      <c r="C94" t="s">
-        <v>86</v>
-      </c>
-      <c r="D94" t="s">
-        <v>87</v>
-      </c>
-      <c r="E94" t="s">
-        <v>20</v>
-      </c>
-      <c r="F94" t="s">
-        <v>37</v>
-      </c>
-      <c r="G94" t="s">
-        <v>77</v>
-      </c>
-      <c r="H94" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B95" t="s">
-        <v>74</v>
-      </c>
-      <c r="C95" t="s">
-        <v>86</v>
-      </c>
-      <c r="D95" t="s">
-        <v>87</v>
-      </c>
-      <c r="E95" t="s">
-        <v>25</v>
-      </c>
-      <c r="F95" t="s">
-        <v>26</v>
-      </c>
-      <c r="G95" t="s">
-        <v>79</v>
-      </c>
-      <c r="H95" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B96" t="s">
-        <v>74</v>
-      </c>
-      <c r="C96" t="s">
-        <v>86</v>
-      </c>
-      <c r="D96" t="s">
-        <v>87</v>
-      </c>
-      <c r="E96" t="s">
-        <v>21</v>
-      </c>
-      <c r="F96" t="s">
-        <v>30</v>
-      </c>
-      <c r="G96" t="s">
-        <v>43</v>
-      </c>
-      <c r="H96" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B97" t="s">
-        <v>74</v>
-      </c>
-      <c r="C97" t="s">
-        <v>86</v>
-      </c>
-      <c r="D97" t="s">
-        <v>87</v>
-      </c>
-      <c r="E97" t="s">
-        <v>22</v>
-      </c>
-      <c r="F97" t="s">
-        <v>32</v>
       </c>
       <c r="G97" t="s">
         <v>44</v>
       </c>
-      <c r="H97" t="s">
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>74</v>
+      </c>
+      <c r="B98" t="s">
+        <v>86</v>
+      </c>
+      <c r="C98" t="s">
+        <v>87</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E98" t="s">
+        <v>34</v>
+      </c>
+      <c r="F98" t="s">
+        <v>35</v>
+      </c>
+      <c r="G98" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>74</v>
+      </c>
+      <c r="B99" t="s">
+        <v>88</v>
+      </c>
+      <c r="C99" t="s">
+        <v>89</v>
+      </c>
+      <c r="D99" t="s">
+        <v>20</v>
+      </c>
+      <c r="E99" t="s">
+        <v>37</v>
+      </c>
+      <c r="F99" t="s">
+        <v>77</v>
+      </c>
+      <c r="G99" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>74</v>
+      </c>
+      <c r="B100" t="s">
+        <v>88</v>
+      </c>
+      <c r="C100" t="s">
+        <v>89</v>
+      </c>
+      <c r="D100" t="s">
+        <v>25</v>
+      </c>
+      <c r="E100" t="s">
+        <v>26</v>
+      </c>
+      <c r="F100" t="s">
+        <v>79</v>
+      </c>
+      <c r="G100" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>74</v>
+      </c>
+      <c r="B101" t="s">
+        <v>88</v>
+      </c>
+      <c r="C101" t="s">
+        <v>89</v>
+      </c>
+      <c r="D101" t="s">
+        <v>21</v>
+      </c>
+      <c r="E101" t="s">
+        <v>30</v>
+      </c>
+      <c r="F101" t="s">
+        <v>43</v>
+      </c>
+      <c r="G101" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>74</v>
+      </c>
+      <c r="B102" t="s">
+        <v>88</v>
+      </c>
+      <c r="C102" t="s">
+        <v>89</v>
+      </c>
+      <c r="D102" t="s">
+        <v>22</v>
+      </c>
+      <c r="E102" t="s">
+        <v>32</v>
+      </c>
+      <c r="F102" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B98" t="s">
-        <v>74</v>
-      </c>
-      <c r="C98" t="s">
-        <v>86</v>
-      </c>
-      <c r="D98" t="s">
-        <v>87</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F98" t="s">
-        <v>34</v>
-      </c>
-      <c r="G98" t="s">
-        <v>35</v>
-      </c>
-      <c r="H98" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B99" t="s">
-        <v>74</v>
-      </c>
-      <c r="C99" t="s">
-        <v>88</v>
-      </c>
-      <c r="D99" t="s">
-        <v>89</v>
-      </c>
-      <c r="E99" t="s">
-        <v>20</v>
-      </c>
-      <c r="F99" t="s">
-        <v>37</v>
-      </c>
-      <c r="G99" t="s">
-        <v>77</v>
-      </c>
-      <c r="H99" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B100" t="s">
-        <v>74</v>
-      </c>
-      <c r="C100" t="s">
-        <v>88</v>
-      </c>
-      <c r="D100" t="s">
-        <v>89</v>
-      </c>
-      <c r="E100" t="s">
-        <v>25</v>
-      </c>
-      <c r="F100" t="s">
-        <v>26</v>
-      </c>
-      <c r="G100" t="s">
-        <v>79</v>
-      </c>
-      <c r="H100" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B101" t="s">
-        <v>74</v>
-      </c>
-      <c r="C101" t="s">
-        <v>88</v>
-      </c>
-      <c r="D101" t="s">
-        <v>89</v>
-      </c>
-      <c r="E101" t="s">
-        <v>21</v>
-      </c>
-      <c r="F101" t="s">
-        <v>30</v>
-      </c>
-      <c r="G101" t="s">
-        <v>43</v>
-      </c>
-      <c r="H101" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B102" t="s">
-        <v>74</v>
-      </c>
-      <c r="C102" t="s">
-        <v>88</v>
-      </c>
-      <c r="D102" t="s">
-        <v>89</v>
-      </c>
-      <c r="E102" t="s">
-        <v>22</v>
-      </c>
-      <c r="F102" t="s">
-        <v>32</v>
       </c>
       <c r="G102" t="s">
         <v>44</v>
       </c>
-      <c r="H102" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>74</v>
+      </c>
       <c r="B103" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C103" t="s">
-        <v>88</v>
-      </c>
-      <c r="D103" t="s">
         <v>89</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="D103" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="E103" t="s">
+        <v>34</v>
+      </c>
       <c r="F103" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G103" t="s">
-        <v>35</v>
-      </c>
-      <c r="H103" t="s">
         <v>50</v>
       </c>
     </row>
